--- a/tame_output/ON/bt/strategyON_20240112.xlsx
+++ b/tame_output/ON/bt/strategyON_20240112.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1839"/>
+  <dimension ref="A1:G1840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.378821167884937</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43858,6 +43858,29 @@
       </c>
       <c r="G1839" t="n">
         <v>4.496515905413327</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="2" t="n">
+        <v>45302</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>3.370022263565001</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>3.156088696795822</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>1.63355912817954</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>3.809155923753891</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>2.236172033896278</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>4.49779191713359</v>
       </c>
     </row>
   </sheetData>
